--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484686_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484686_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6044</v>
+        <v>4.6679</v>
       </c>
       <c r="E2" t="n">
-        <v>4.607</v>
+        <v>4.621</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0026</v>
+        <v>0.0469</v>
       </c>
       <c r="G2" t="n">
         <v>5.8089</v>
@@ -610,13 +610,13 @@
         <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1495</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1297</v>
+        <v>-0.1157</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0198</v>
+        <v>0.0298</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3219</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3315</v>
+        <v>3.3198</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0851</v>
+        <v>2.4697</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2465</v>
+        <v>0.8501</v>
       </c>
       <c r="G3" t="n">
         <v>3.0279</v>
@@ -688,13 +688,13 @@
         <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.207</v>
+        <v>-0.2187</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7157</v>
+        <v>-0.3311</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5087</v>
+        <v>0.1123</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9554</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>E. NAVARRO VALDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5833</v>
+        <v>1.1129</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8001</v>
+        <v>2.3762</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3834</v>
+        <v>-1.2632</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3117</v>
+        <v>3.2853</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5263</v>
+        <v>0.1116</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2146</v>
+        <v>3.1736</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0167</v>
+        <v>4.7586</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9418</v>
+        <v>1.8732</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9585</v>
+        <v>2.8854</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3284</v>
+        <v>-1.4733</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5845</v>
+        <v>-1.7615</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2561</v>
+        <v>0.2882</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.4661</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9321</v>
+        <v>-2.0158</v>
       </c>
       <c r="R6" t="n">
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>3.039</v>
+        <v>-0.9891</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7934</v>
+        <v>-0.6885</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2457</v>
+        <v>-0.3005</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3219</v>
+        <v>-0.6335</v>
       </c>
       <c r="W6" t="n">
         <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDES</t>
+          <t>E. CIRCUNS RIVERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4637</v>
+        <v>0.1102</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0737</v>
+        <v>2.299</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6101</v>
+        <v>-2.1888</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2853</v>
+        <v>1.9732</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1116</v>
+        <v>-2.0918</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1736</v>
+        <v>4.065</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7586</v>
+        <v>4.1105</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8732</v>
+        <v>-0.4676</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8854</v>
+        <v>4.5781</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4733</v>
+        <v>-2.1373</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7615</v>
+        <v>-1.6241</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2882</v>
+        <v>-0.5131</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5498</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0158</v>
+        <v>-2.9321</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6383</v>
+        <v>-0.3524</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9909</v>
+        <v>-0.4683</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6474</v>
+        <v>0.1159</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6335</v>
+        <v>0.3219</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9554</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. CIRCUNS RIVERA</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4702</v>
+        <v>-1.0436</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9415</v>
+        <v>-1.9811</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4117</v>
+        <v>0.9374</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9732</v>
+        <v>-1.3117</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0918</v>
+        <v>-2.5263</v>
       </c>
       <c r="I8" t="n">
-        <v>4.065</v>
+        <v>1.2146</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1105</v>
+        <v>0.0167</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4676</v>
+        <v>-0.9418</v>
       </c>
       <c r="L8" t="n">
-        <v>4.5781</v>
+        <v>0.9585</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1373</v>
+        <v>-1.3284</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6241</v>
+        <v>-1.5845</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5131</v>
+        <v>0.2561</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8326</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.9321</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9328</v>
+        <v>1.4121</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8258</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.107</v>
+        <v>0.7997</v>
       </c>
       <c r="V8" t="n">
         <v>0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6118</v>
+        <v>-1.8348</v>
       </c>
       <c r="E9" t="n">
         <v>-0.2238</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.388</v>
+        <v>-1.611</v>
       </c>
       <c r="G9" t="n">
         <v>0.7374000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5325</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>-0.4404</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0921</v>
+        <v>-0.3151</v>
       </c>
       <c r="V9" t="n">
         <v>-1.267</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1159</v>
+        <v>-1.8711</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1783</v>
+        <v>0.2745</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2943</v>
+        <v>-2.1456</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1864</v>
@@ -1234,13 +1234,13 @@
         <v>0.1833</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1541</v>
+        <v>0.3989</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0551</v>
+        <v>0.0411</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2092</v>
+        <v>0.3578</v>
       </c>
       <c r="V10" t="n">
         <v>-1.267</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3846</v>
+        <v>-2.1947</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1081</v>
+        <v>-0.9429</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2765</v>
+        <v>-1.2517</v>
       </c>
       <c r="G11" t="n">
         <v>1.276</v>
@@ -1312,13 +1312,13 @@
         <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4224</v>
+        <v>-0.2325</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.405</v>
+        <v>-0.2398</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0175</v>
+        <v>0.0073</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5889</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1535</v>
+        <v>-3.5459</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.526</v>
+        <v>-3.1413</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.4046</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5797</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.291</v>
+        <v>0.3165</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4404</v>
+        <v>-0.0558</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1494</v>
+        <v>0.3723</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1351</v>
+        <v>-4.7832</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5113</v>
+        <v>-4.2089</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6238</v>
+        <v>-0.5743</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7308</v>
@@ -1468,13 +1468,13 @@
         <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3885</v>
+        <v>-0.0366</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5505</v>
+        <v>-0.2481</v>
       </c>
       <c r="U13" t="n">
-        <v>0.162</v>
+        <v>0.2115</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.412400000000001</v>
+        <v>-2.586700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>4.192099999999998</v>
+        <v>5.0182</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.6046</v>
+        <v>-7.6048</v>
       </c>
       <c r="G14" t="n">
         <v>13.7759</v>
@@ -1546,13 +1546,13 @@
         <v>10.0792</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3689</v>
+        <v>-0.5433</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.7601</v>
+        <v>-1.9342</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3912</v>
+        <v>1.391</v>
       </c>
       <c r="V14" t="n">
         <v>-6.6569</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2463</v>
+        <v>3.6257</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3036</v>
+        <v>4.5344</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0573</v>
+        <v>-0.9086</v>
       </c>
       <c r="G15" t="n">
         <v>0.5468</v>
@@ -1624,13 +1624,13 @@
         <v>2.3823</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2884</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1147</v>
+        <v>0.3454</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1737</v>
+        <v>0.3224</v>
       </c>
       <c r="V15" t="n">
         <v>0.945</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.649</v>
+        <v>2.5946</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0042</v>
+        <v>2.6773</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3552</v>
+        <v>-0.0827</v>
       </c>
       <c r="G16" t="n">
         <v>-2.6964</v>
@@ -1702,13 +1702,13 @@
         <v>3.1154</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3877</v>
+        <v>0.5579</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.2085</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4939</v>
+        <v>0.7664</v>
       </c>
       <c r="V16" t="n">
         <v>2.5339</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5566</v>
+        <v>1.8975</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1619</v>
+        <v>1.3542</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3947</v>
+        <v>0.5433</v>
       </c>
       <c r="G17" t="n">
         <v>0.0291</v>
@@ -1780,13 +1780,13 @@
         <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6716</v>
+        <v>-0.3307</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7526</v>
+        <v>-0.5603</v>
       </c>
       <c r="U17" t="n">
-        <v>0.081</v>
+        <v>0.2296</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3688</v>
+        <v>1.8218</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1568</v>
+        <v>1.7338</v>
       </c>
       <c r="F18" t="n">
-        <v>0.212</v>
+        <v>0.0881</v>
       </c>
       <c r="G18" t="n">
         <v>-2.5381</v>
@@ -1858,13 +1858,13 @@
         <v>2.3823</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3759</v>
+        <v>0.0771</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8635</v>
+        <v>-0.2865</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4875</v>
+        <v>0.3637</v>
       </c>
       <c r="V18" t="n">
         <v>1.9005</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. POVEDA CASTELLO</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5908</v>
+        <v>0.7048</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2977</v>
+        <v>0.3967</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2932</v>
+        <v>0.3081</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.6096</v>
+        <v>0.5003</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5995</v>
+        <v>-0.1407</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.0101</v>
+        <v>0.641</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8401999999999999</v>
+        <v>2.7583</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2666</v>
+        <v>1.3156</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5736</v>
+        <v>1.4427</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7694</v>
+        <v>-2.2579</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3329</v>
+        <v>-1.4563</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.4365</v>
+        <v>-0.8017</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1991</v>
+        <v>2.7489</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8394</v>
+        <v>-0.3899</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9759</v>
+        <v>-0.529</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8635</v>
+        <v>0.1391</v>
       </c>
       <c r="V19" t="n">
-        <v>1.9109</v>
+        <v>-0.3219</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1745</v>
+        <v>-0.0697</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.08409999999999999</v>
+        <v>2.1586</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2586</v>
+        <v>-2.2283</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5003</v>
+        <v>-1.4071</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1407</v>
+        <v>-2.0771</v>
       </c>
       <c r="I20" t="n">
-        <v>0.641</v>
+        <v>0.67</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7583</v>
+        <v>1.9162</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3156</v>
+        <v>-0.0683</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4427</v>
+        <v>1.9845</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2579</v>
+        <v>-3.3232</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4563</v>
+        <v>-2.0088</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8017</v>
+        <v>-1.3145</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7489</v>
+        <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9202</v>
+        <v>-0.4402</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0098</v>
+        <v>-0.391</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0896</v>
+        <v>-0.0492</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3219</v>
+        <v>0.3115</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X20" t="n">
         <v>-0.3219</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>M. POVEDA CASTELLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1848</v>
+        <v>-0.9069</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8702</v>
+        <v>-0.9523</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0549</v>
+        <v>0.0454</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4071</v>
+        <v>-3.6096</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0771</v>
+        <v>-0.5995</v>
       </c>
       <c r="I21" t="n">
-        <v>0.67</v>
+        <v>-3.0101</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9162</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0683</v>
+        <v>-0.2666</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9845</v>
+        <v>-0.5736</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3232</v>
+        <v>-2.7694</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0088</v>
+        <v>-0.3329</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3145</v>
+        <v>-2.4365</v>
       </c>
       <c r="P21" t="n">
-        <v>1.4661</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4661</v>
+        <v>2.1991</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5553</v>
+        <v>1.3416</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6795</v>
+        <v>0.7259</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1242</v>
+        <v>0.6157</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3115</v>
+        <v>1.9109</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6335</v>
+        <v>1.9109</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3077</v>
+        <v>-1.9153</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4249</v>
+        <v>-1.8096</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1173</v>
+        <v>-0.1057</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1673</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8596</v>
+        <v>0.2521</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3107</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.326</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6811</v>
+        <v>-4.3401</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6806</v>
+        <v>-2.4883</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0005</v>
+        <v>-1.8518</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4339</v>
@@ -2248,13 +2248,13 @@
         <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7078</v>
+        <v>-0.3669</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6056</v>
+        <v>-0.4133</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1023</v>
+        <v>0.0464</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6231</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.412399999999999</v>
+        <v>3.412400000000001</v>
       </c>
       <c r="E24" t="n">
         <v>7.604799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.1921</v>
+        <v>-4.1922</v>
       </c>
       <c r="G24" t="n">
         <v>-13.7762</v>
@@ -2311,7 +2311,7 @@
         <v>-23.6396</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.770200000000001</v>
+        <v>-7.7702</v>
       </c>
       <c r="O24" t="n">
         <v>-15.8696</v>
@@ -2326,13 +2326,13 @@
         <v>19.2421</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3689</v>
+        <v>1.3688</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3913</v>
+        <v>-1.3912</v>
       </c>
       <c r="U24" t="n">
-        <v>2.76</v>
+        <v>2.7601</v>
       </c>
       <c r="V24" t="n">
         <v>6.6568</v>
